--- a/data/merged/2026-09-28/MERGED_IT_Spot-Cleaner_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_IT_Spot-Cleaner_2026-09-28.xlsx
@@ -5874,13 +5874,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5917,13 +5917,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6005,13 +6005,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6137,14 +6137,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6182,13 +6182,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6205,94 +6205,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId33" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Product 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Product 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6634,7 +6546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -14579,285 +14491,35 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0GM1PQ8M8</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>Nome stile: Oxygen Boost</t>
+          <t>Colore: Dune | Taglia: Clean It</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Bissell | Forma articolo: Liquido | Fragranza: Fresco | Usi specifici del prodotto: Moquette | Caratteristica del materiale: Riciclabile | Volume articolo: 1 Litri | Conteggio unità: 1000.0 Millilitri | Superfici consigliate: Tessuto | Caratteristica speciale: Multiuso, Non lascia residui, Senza risciacquo | Numero di articoli: 1</t>
+          <t>Marchio: Rowenta | Colore: Dune | Peso articolo: 4,09 Chilogrammi | Nome modello: Clean It | Capacità: 1,4 litri</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>Rowenta</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/Rowenta/page/2FFCA3F5-1E5B-4BD9-BDC6-F0C2B3DB287C?lp_asin=B0GM1PQ8M8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Potenziatore Detergente 1 L 1134N</t>
+          <t>Rowenta Clean It, Smacchiatore Compatto, IN3010</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>RIMUOVE IN MODO PERMANENTE LE MACCHIE OSTINATE: Da utilizzare in combinazione con la tua soluzione detergente BISSELL preferita per la pulizia profonda per rimuovere le macchie da moquette, rivestimenti, tappeti e altro
-DISTRUGGE LE MACCHIE CON OXY: Rimuove in modo permanente le macchie ostinate causate da sporco domestico e animali.
-ADDITIVO SICURO PER LE MACCHINE: Sicuro da usare con soluzioni e dispositivi per la pulizia profonda portatili e verticali BISSELL, e compatibile con altri pulitori principali per moquette e rivestimenti, se usato secondo istruzioni.
-SICURO SE USATO SECONDO LE ISTRUZIONI: Sicuro da usare in presenza di bambini e animali domestici, se usato secondo istruzioni.
-OGNI ACQUISTO SALVA UN ANIMALE: Ogni acquisto consente a BISSELL di continuare a sostenere la BISSELL PET Foundation e la sua missione di salvare animali.</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0753NXDPR?psc=1</t>
-        </is>
-      </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/31BhvLWbbNL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L33" s="14" t="inlineStr">
-        <is>
-          <t>B0DJWC9K1G</t>
-        </is>
-      </c>
-      <c r="M33" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O33" s="15">
-        <v>2459</v>
-      </c>
-      <c r="P33" s="15">
-        <v>639</v>
-      </c>
-      <c r="Q33" s="16">
-        <v>0.35</v>
-      </c>
-      <c r="R33" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti
-Detergenti e prodotti per la pulizia</t>
-        </is>
-      </c>
-      <c r="S33" s="18" t="inlineStr">
-        <is>
-          <t>6
-76</t>
-        </is>
-      </c>
-      <c r="T33" s="15">
-        <v>846</v>
-      </c>
-      <c r="U33" s="16">
-        <v>0.31</v>
-      </c>
-      <c r="V33" s="15">
-        <v>12682</v>
-      </c>
-      <c r="W33" s="15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="X33" s="15">
-        <v>2998</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>4</v>
-      </c>
-      <c r="Z33" s="20">
-        <v>14.99</v>
-      </c>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD33" s="19">
-        <v>9418</v>
-      </c>
-      <c r="AE33" s="15">
-        <v>217</v>
-      </c>
-      <c r="AF33" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG33" s="22">
-        <v>0.2565</v>
-      </c>
-      <c r="AH33" s="20">
-        <v>5.19</v>
-      </c>
-      <c r="AI33" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="AJ33"/>
-      <c r="AK33" s="13" t="inlineStr">
-        <is>
-          <t>2017-10-06</t>
-        </is>
-      </c>
-      <c r="AL33" s="19">
-        <v>3279</v>
-      </c>
-      <c r="AM33" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN33" s="13"/>
-      <c r="AO33" s="13"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR33" s="19">
-        <v>8</v>
-      </c>
-      <c r="AS33" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT33" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU33" s="13"/>
-      <c r="AV33" s="14"/>
-      <c r="AW33" s="13"/>
-      <c r="AX33" s="13"/>
-      <c r="AY33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ33" s="13"/>
-      <c r="BA33" s="13"/>
-      <c r="BB33" s="13"/>
-      <c r="BC33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE33" s="13"/>
-      <c r="BF33" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG33" s="13"/>
-      <c r="BH33" s="14"/>
-      <c r="BI33" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ33" s="23" t="inlineStr">
-        <is>
-          <t>1,1 kg</t>
-        </is>
-      </c>
-      <c r="BK33" s="23" t="inlineStr">
-        <is>
-          <t>1.10 kg</t>
-        </is>
-      </c>
-      <c r="BL33" s="23" t="inlineStr">
-        <is>
-          <t>7 x 12 x 23,8 cm</t>
-        </is>
-      </c>
-      <c r="BM33" s="23" t="inlineStr">
-        <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
-        </is>
-      </c>
-      <c r="BN33" s="23" t="inlineStr">
-        <is>
-          <t>1.1 kg</t>
-        </is>
-      </c>
-      <c r="BO33" s="23" t="inlineStr">
-        <is>
-          <t>1.10 kg</t>
-        </is>
-      </c>
-      <c r="BP33" s="23" t="inlineStr">
-        <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ33" s="23" t="inlineStr">
-        <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
-        </is>
-      </c>
-      <c r="BR33" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13">
-        <v>33</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>B0GM1PQ8M8</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Colore: Dune | Taglia: Clean It</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Rowenta | Colore: Dune | Peso articolo: 4,09 Chilogrammi | Nome modello: Clean It | Capacità: 1,4 litri</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Rowenta</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Rowenta/page/2FFCA3F5-1E5B-4BD9-BDC6-F0C2B3DB287C?lp_asin=B0GM1PQ8M8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>Rowenta Clean It, Smacchiatore Compatto, IN3010</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>PULIZIA QUOTIDIANA FACILE E VELOCE: Scopri uno smacchiatore efficace e rapido, ideale per affrontare quotidianamente sporco e macchie causati da animali, incidenti domestici e molto altro
 IL PIÙ COMPATTO DI ROWENTA: Pulizia impeccabile sempre a portata di mano, grazie al design compatto e leggero che si ripone con facilità ovunque
@@ -14866,19 +14528,235 @@
 RIPARABILITÀ DI 15 ANNI AD UN PREZZO EQUO: Consigliamo di riparare il prodotto presso la nostra rete di 6.200 centri di riparazione in tutto il mondo, per una durata ancora più lunga SOLUZIONE DETERGENTE UNIVERSALE: Basta spruzzarla direttamente su sporco e macchie quotidiane per ottenere una pulizia profonda accompagnata da una piacevole fragranza</t>
         </is>
       </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/dp/B0GM1PQ8M8?psc=1</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41bb8efrOAL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>B0HCWGMQKH</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
+        </is>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+        </is>
+      </c>
+      <c r="O33" s="15">
+        <v>18045</v>
+      </c>
+      <c r="P33" s="15">
+        <v>2439</v>
+      </c>
+      <c r="Q33" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>Lavatappeti</t>
+        </is>
+      </c>
+      <c r="S33" s="18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="T33" s="15">
+        <v>125</v>
+      </c>
+      <c r="U33" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="V33" s="15">
+        <v>12499</v>
+      </c>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="19">
+        <v>4</v>
+      </c>
+      <c r="Z33" s="20">
+        <v>99.99</v>
+      </c>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="19">
+        <v>11</v>
+      </c>
+      <c r="AE33" s="15">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="21">
+        <v>4.4</v>
+      </c>
+      <c r="AG33" s="22">
+        <v>0.008</v>
+      </c>
+      <c r="AH33" s="20">
+        <v>9.57</v>
+      </c>
+      <c r="AI33" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="AJ33"/>
+      <c r="AK33" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AL33" s="19">
+        <v>207</v>
+      </c>
+      <c r="AM33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN33" s="13"/>
+      <c r="AO33" s="13"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="19">
+        <v>6</v>
+      </c>
+      <c r="AR33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS33" s="14" t="inlineStr">
+        <is>
+          <t>Home &amp; Cook - Italia</t>
+        </is>
+      </c>
+      <c r="AT33" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU33" s="13" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="AV33" s="14" t="inlineStr">
+        <is>
+          <t>MILANO 20156 IT</t>
+        </is>
+      </c>
+      <c r="AW33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KISR7QA7WRPG</t>
+        </is>
+      </c>
+      <c r="AX33" s="13"/>
+      <c r="AY33" s="13"/>
+      <c r="AZ33" s="13"/>
+      <c r="BA33" s="13"/>
+      <c r="BB33" s="13"/>
+      <c r="BC33" s="13"/>
+      <c r="BD33" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE33" s="13"/>
+      <c r="BF33" s="13"/>
+      <c r="BG33" s="13"/>
+      <c r="BH33" s="14"/>
+      <c r="BI33" s="23"/>
+      <c r="BJ33" s="23" t="inlineStr">
+        <is>
+          <t>4,09 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK33" s="23"/>
+      <c r="BL33" s="23" t="inlineStr">
+        <is>
+          <t>38,5 x 37,2 x 28,2 cm</t>
+        </is>
+      </c>
+      <c r="BM33" s="23" t="inlineStr">
+        <is>
+          <t>38.50 x 37.20 x 28.20 cm</t>
+        </is>
+      </c>
+      <c r="BN33" s="23" t="inlineStr">
+        <is>
+          <t>6.27 kg</t>
+        </is>
+      </c>
+      <c r="BO33" s="23" t="inlineStr">
+        <is>
+          <t>6.27 kg</t>
+        </is>
+      </c>
+      <c r="BP33" s="23" t="inlineStr">
+        <is>
+          <t>40.2 x 39.9 x 29.4 cm</t>
+        </is>
+      </c>
+      <c r="BQ33" s="23" t="inlineStr">
+        <is>
+          <t>40.20 x 39.90 x 29.40 cm</t>
+        </is>
+      </c>
+      <c r="BR33" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>B0BSHCQQ4W</t>
+        </is>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>H.Koenig</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
+        </is>
+      </c>
+      <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GM1PQ8M8?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41bb8efrOAL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0HCWGMQKH</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -14888,17 +14766,17 @@
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O34" s="15">
-        <v>18045</v>
+        <v>42508</v>
       </c>
       <c r="P34" s="15">
-        <v>2439</v>
+        <v>-13953</v>
       </c>
       <c r="Q34" s="16">
-        <v>0.18</v>
+        <v>-0.49</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -14907,101 +14785,115 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>54</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="U34" s="16">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="V34" s="15">
-        <v>12499</v>
-      </c>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
+        <v>10787</v>
+      </c>
+      <c r="W34" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X34" s="15">
+        <v>3845</v>
+      </c>
       <c r="Y34" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z34" s="20">
-        <v>99.99</v>
+        <v>79.9</v>
       </c>
       <c r="AA34" s="4"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>11</v>
+        <v>1085</v>
       </c>
       <c r="AE34" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.008</v>
+        <v>0.037000000000000005</v>
       </c>
       <c r="AH34" s="20">
-        <v>9.57</v>
+        <v>9.79</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>207</v>
+        <v>1310</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
       <c r="AO34" s="13"/>
       <c r="AP34" s="4"/>
       <c r="AQ34" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Home &amp; Cook - Italia</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU34" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV34" s="14" t="inlineStr">
         <is>
-          <t>MILANO 20156 IT</t>
+          <t>Paris 75001 FR</t>
         </is>
       </c>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KISR7QA7WRPG</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
-      <c r="AY34" s="13"/>
+      <c r="AY34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
-      <c r="BC34" s="13"/>
+      <c r="BC34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD34" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15011,41 +14903,49 @@
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
       <c r="BH34" s="14"/>
-      <c r="BI34" s="23"/>
+      <c r="BI34" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>4,09 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK34" s="23"/>
+          <t>4 kg</t>
+        </is>
+      </c>
+      <c r="BK34" s="23" t="inlineStr">
+        <is>
+          <t>4.00 kg</t>
+        </is>
+      </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>38,5 x 37,2 x 28,2 cm</t>
+          <t>36.5 x 24.5 x 31.8 cm</t>
         </is>
       </c>
       <c r="BM34" s="23" t="inlineStr">
         <is>
-          <t>38.50 x 37.20 x 28.20 cm</t>
+          <t>36.50 x 24.50 x 31.80 cm</t>
         </is>
       </c>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>6.27 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>6.27 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>40.2 x 39.9 x 29.4 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>40.20 x 39.90 x 29.40 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
@@ -15061,273 +14961,35 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
-        </is>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
+          <t>B0CXMC73YV</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Nome stile: Animali</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Marchio: Shark | Colore: Rotator White | Peso articolo: 4,2 Chilogrammi | Dimensioni del prodotto: 28P x 29,8l x 28,7H cm | Stile: Animali</t>
+        </is>
+      </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0CXMC73YV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
-        </is>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
-        </is>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L35" s="14" t="inlineStr">
-        <is>
-          <t>B0BSHCQQ4W</t>
-        </is>
-      </c>
-      <c r="M35" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O35" s="15">
-        <v>42508</v>
-      </c>
-      <c r="P35" s="15">
-        <v>-13953</v>
-      </c>
-      <c r="Q35" s="16">
-        <v>-0.49</v>
-      </c>
-      <c r="R35" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S35" s="18" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="T35" s="15">
-        <v>135</v>
-      </c>
-      <c r="U35" s="16">
-        <v>1.32</v>
-      </c>
-      <c r="V35" s="15">
-        <v>10787</v>
-      </c>
-      <c r="W35" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X35" s="15">
-        <v>3845</v>
-      </c>
-      <c r="Y35" s="19">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="20">
-        <v>79.9</v>
-      </c>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="2"/>
-      <c r="AD35" s="19">
-        <v>1085</v>
-      </c>
-      <c r="AE35" s="15">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG35" s="22">
-        <v>0.037000000000000005</v>
-      </c>
-      <c r="AH35" s="20">
-        <v>9.79</v>
-      </c>
-      <c r="AI35" s="16">
-        <v>0.73</v>
-      </c>
-      <c r="AJ35"/>
-      <c r="AK35" s="13" t="inlineStr">
-        <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AL35" s="19">
-        <v>1310</v>
-      </c>
-      <c r="AM35" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="13"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR35" s="19">
-        <v>7</v>
-      </c>
-      <c r="AS35" s="14" t="inlineStr">
-        <is>
-          <t>HomeHome by A</t>
-        </is>
-      </c>
-      <c r="AT35" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU35" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV35" s="14" t="inlineStr">
-        <is>
-          <t>Paris 75001 FR</t>
-        </is>
-      </c>
-      <c r="AW35" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
-        </is>
-      </c>
-      <c r="AX35" s="13"/>
-      <c r="AY35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ35" s="13"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="14"/>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ35" s="23" t="inlineStr">
-        <is>
-          <t>4 kg</t>
-        </is>
-      </c>
-      <c r="BK35" s="23" t="inlineStr">
-        <is>
-          <t>4.00 kg</t>
-        </is>
-      </c>
-      <c r="BL35" s="23" t="inlineStr">
-        <is>
-          <t>36.5 x 24.5 x 31.8 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23" t="inlineStr">
-        <is>
-          <t>36.50 x 24.50 x 31.80 cm</t>
-        </is>
-      </c>
-      <c r="BN35" s="23" t="inlineStr">
-        <is>
-          <t>5.88 kg</t>
-        </is>
-      </c>
-      <c r="BO35" s="23" t="inlineStr">
-        <is>
-          <t>5.88 kg</t>
-        </is>
-      </c>
-      <c r="BP35" s="23" t="inlineStr">
-        <is>
-          <t>45 x 38 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BQ35" s="23" t="inlineStr">
-        <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BR35" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>B0CXMC73YV</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Nome stile: Animali</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Shark | Colore: Rotator White | Peso articolo: 4,2 Chilogrammi | Dimensioni del prodotto: 28P x 29,8l x 28,7H cm | Stile: Animali</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Shark</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0CXMC73YV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
           <t>Shark StainStriker, Pulitore Tappezzeria e Smacchiatore, 5 Accessori, 450W</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>ELIMINATORE DI MACCHIE E ODORI POTENZIATO: Il pulitore compatto rimuove istantaneamente macchie e odori da tappeti, moquette, scale, tappezzeria, interni di auto e altro ancora
 SOLUZIONE DI PULIZIA A DOPPIA ATTIVAZIONE: I detergenti Shark CarpetXpert Deep Clean Pro e StainStriker Oxy Multiplier si combinano e si attivano per rimuovere sporco, incrostazioni, macchie e odori. Non è necessario alcun pretrattamento
@@ -15337,19 +14999,257 @@
 Garanzia di 3 anni al momento della registrazione su Shark</t>
         </is>
       </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/dp/B0CXMC73YV?psc=1</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41yDeV+UoOL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>B0H63GF4QX</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
+        </is>
+      </c>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+        </is>
+      </c>
+      <c r="O35" s="15">
+        <v>19210</v>
+      </c>
+      <c r="P35" s="15">
+        <v>14706</v>
+      </c>
+      <c r="Q35" s="16">
+        <v>0.37</v>
+      </c>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <t>Lavatappeti</t>
+        </is>
+      </c>
+      <c r="S35" s="18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T35" s="15">
+        <v>77</v>
+      </c>
+      <c r="U35" s="16">
+        <v>-0.03</v>
+      </c>
+      <c r="V35" s="15">
+        <v>10053</v>
+      </c>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="20">
+        <v>99.09</v>
+      </c>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="19">
+        <v>595</v>
+      </c>
+      <c r="AE35" s="15">
+        <v>7</v>
+      </c>
+      <c r="AF35" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="AG35" s="22">
+        <v>0.0909</v>
+      </c>
+      <c r="AH35" s="20">
+        <v>9.35</v>
+      </c>
+      <c r="AI35" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="AJ35"/>
+      <c r="AK35" s="13" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AL35" s="19">
+        <v>894</v>
+      </c>
+      <c r="AM35" s="13" t="inlineStr">
+        <is>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AN35" s="13" t="inlineStr">
+        <is>
+          <t>15-26天</t>
+        </is>
+      </c>
+      <c r="AO35" s="13"/>
+      <c r="AP35" s="4">
+        <v>72.73</v>
+      </c>
+      <c r="AQ35" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR35" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="AT35" s="13" t="inlineStr">
+        <is>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU35" s="13"/>
+      <c r="AV35" s="14"/>
+      <c r="AW35" s="13"/>
+      <c r="AX35" s="13"/>
+      <c r="AY35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ35" s="13"/>
+      <c r="BA35" s="13"/>
+      <c r="BB35" s="13"/>
+      <c r="BC35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE35" s="13"/>
+      <c r="BF35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG35" s="13"/>
+      <c r="BH35" s="14"/>
+      <c r="BI35" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
+      <c r="BJ35" s="23" t="inlineStr">
+        <is>
+          <t>4,2 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK35" s="23"/>
+      <c r="BL35" s="23" t="inlineStr">
+        <is>
+          <t>28P x 29,8l x 28,7H cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="23"/>
+      <c r="BN35" s="23" t="inlineStr">
+        <is>
+          <t>6.76 kg</t>
+        </is>
+      </c>
+      <c r="BO35" s="23" t="inlineStr">
+        <is>
+          <t>6.76 kg</t>
+        </is>
+      </c>
+      <c r="BP35" s="23" t="inlineStr">
+        <is>
+          <t>39 x 35 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BQ35" s="23" t="inlineStr">
+        <is>
+          <t>39.00 x 35.00 x 31.00 cm</t>
+        </is>
+      </c>
+      <c r="BR35" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
+        <v>35</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>B0DT7CPRW2</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Nome stile: StainStriker HairPro – Animali</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Marchio: Shark | Colore: Argento Scuro E Fucsia Forzato | Peso articolo: 4,6 Chilogrammi | Dimensioni del prodotto: 36,5P x 29,4l x 38,1H cm | Stile: StainStriker HairPro – Animali</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Shark</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Shark StainStriker HairPro Pet, Pulitore con Aspirazione, 4 Accessori, 450W</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>IDEATO PER CASE CON ANIMALI DOMESTICI: Pulitore leggero che elimina sporco, macchie e odori ostinati di animali domestici, come quello di urina. Non richiede riscaldamento o pre-riscaldamento. Perfetto per moquette, tappeti e tappezzeria
+APIRAZIONE POTENTE: La tecnologia anti-intasamento, anti-agglomerazione e anti-groviglio invia i peli direttamente nel serbatoio dell'acqua sporca, evitando di intasare l'apparecchio, aggrovigliare gli accessori o lasciare grumi di peli bagnati
+SOLUZIONE A DOPPIA ATTIVAZIONE: Due formulazioni per un’efficacia 20 volte superiore* (*In base a test sulla velocità di sublimazione dello iodio; CarpetXpert Deep Clean Pro e StainStriker Oxy Multiplier rispetto a CarpetXpert Deep Clean Pro)
+POTENTE ASPIRAZIONE SHARK: Lo spray ad alta pressione pulisce le fibre in profondità. L'aspirazione potente estrae sporco e liquidi per un'asciugatura rapida. Rimuove macchie e odori, residui di cibo e liquidi, fango e sporco incrostato
+INCLUDE: StainStriker HairPro Pet (spina UE), Accessorio Macchie Ostinate, Bocchetta per Fessure, Estrattore Peli, Accessorio Per Macchie di Animali, Soluzione CarpetXpert Deep Clean Pet (177 ml) e Soluzione StainStriker OXY Multiplier (355 ml)</t>
+        </is>
+      </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CXMC73YV?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DT7CPRW2?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41yDeV+UoOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0H63GF4QX</t>
+          <t>B0H6JYXV4D</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -15363,13 +15263,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>19210</v>
+        <v>18064</v>
       </c>
       <c r="P36" s="15">
-        <v>14706</v>
+        <v>-888</v>
       </c>
       <c r="Q36" s="16">
-        <v>0.37</v>
+        <v>-0.01</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -15378,75 +15278,69 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="U36" s="16">
-        <v>-0.03</v>
+        <v>1.14</v>
       </c>
       <c r="V36" s="15">
-        <v>10053</v>
+        <v>9449</v>
       </c>
       <c r="W36" s="15"/>
       <c r="X36" s="15"/>
       <c r="Y36" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z36" s="20">
-        <v>99.09</v>
+        <v>149.99</v>
       </c>
       <c r="AA36" s="4"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>595</v>
+        <v>146</v>
       </c>
       <c r="AE36" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0909</v>
+        <v>0.1746</v>
       </c>
       <c r="AH36" s="20">
         <v>9.35</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>894</v>
+        <v>580</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN36" s="13" t="inlineStr">
-        <is>
-          <t>15-26天</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
-      <c r="AP36" s="4">
-        <v>72.73</v>
-      </c>
+      <c r="AP36" s="4"/>
       <c r="AQ36" s="19">
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
@@ -15455,7 +15349,7 @@
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU36" s="13"/>
@@ -15495,34 +15389,34 @@
       </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>4,2 Chilogrammi</t>
+          <t>4,6 Chilogrammi</t>
         </is>
       </c>
       <c r="BK36" s="23"/>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>28P x 29,8l x 28,7H cm</t>
+          <t>36,5P x 29,4l x 38,1H cm</t>
         </is>
       </c>
       <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>6.76 kg</t>
+          <t>6.98 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>6.76 kg</t>
+          <t>6.98 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>39 x 35 x 31 cm</t>
+          <t>39.4 x 35.7 x 31.4 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>39.00 x 35.00 x 31.00 cm</t>
+          <t>39.40 x 35.70 x 31.40 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -15538,56 +15432,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0DT7CPRW2</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Nome stile: StainStriker HairPro – Animali</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Shark | Colore: Argento Scuro E Fucsia Forzato | Peso articolo: 4,6 Chilogrammi | Dimensioni del prodotto: 36,5P x 29,4l x 38,1H cm | Stile: StainStriker HairPro – Animali</t>
-        </is>
-      </c>
+          <t>B0CLYF3DMZ</t>
+        </is>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>LEHMANN</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker HairPro Pet, Pulitore con Aspirazione, 4 Accessori, 450W</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>IDEATO PER CASE CON ANIMALI DOMESTICI: Pulitore leggero che elimina sporco, macchie e odori ostinati di animali domestici, come quello di urina. Non richiede riscaldamento o pre-riscaldamento. Perfetto per moquette, tappeti e tappezzeria
-APIRAZIONE POTENTE: La tecnologia anti-intasamento, anti-agglomerazione e anti-groviglio invia i peli direttamente nel serbatoio dell'acqua sporca, evitando di intasare l'apparecchio, aggrovigliare gli accessori o lasciare grumi di peli bagnati
-SOLUZIONE A DOPPIA ATTIVAZIONE: Due formulazioni per un’efficacia 20 volte superiore* (*In base a test sulla velocità di sublimazione dello iodio; CarpetXpert Deep Clean Pro e StainStriker Oxy Multiplier rispetto a CarpetXpert Deep Clean Pro)
-POTENTE ASPIRAZIONE SHARK: Lo spray ad alta pressione pulisce le fibre in profondità. L'aspirazione potente estrae sporco e liquidi per un'asciugatura rapida. Rimuove macchie e odori, residui di cibo e liquidi, fango e sporco incrostato
-INCLUDE: StainStriker HairPro Pet (spina UE), Accessorio Macchie Ostinate, Bocchetta per Fessure, Estrattore Peli, Accessorio Per Macchie di Animali, Soluzione CarpetXpert Deep Clean Pet (177 ml) e Soluzione StainStriker OXY Multiplier (355 ml)</t>
-        </is>
-      </c>
+          <t>LEHMANN Prowash Lavatappeti Professionale, 2000 W, Lava Tappezzeria Potente con 2 Serbatoi - Acqua Pulita 3L e Sporca 1,5L, T</t>
+        </is>
+      </c>
+      <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DT7CPRW2?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CLYF3DMZ?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0H6JYXV4D</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15597,17 +15475,17 @@
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O37" s="15">
-        <v>18064</v>
+        <v>66356</v>
       </c>
       <c r="P37" s="15">
-        <v>-888</v>
+        <v>-78489</v>
       </c>
       <c r="Q37" s="16">
-        <v>-0.01</v>
+        <v>-1.25</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15616,59 +15494,59 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U37" s="16">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="V37" s="15">
-        <v>9449</v>
+        <v>8059</v>
       </c>
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
       <c r="Y37" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>149.99</v>
+        <v>129.99</v>
       </c>
       <c r="AA37" s="4"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>146</v>
+        <v>386</v>
       </c>
       <c r="AE37" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.1746</v>
+        <v>0.1935</v>
       </c>
       <c r="AH37" s="20">
-        <v>9.35</v>
+        <v>10.24</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>580</v>
+        <v>921</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
@@ -15678,21 +15556,33 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU37" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV37" s="14" t="inlineStr">
+        <is>
+          <t>Greater Poland 63-100 PL</t>
+        </is>
+      </c>
+      <c r="AW37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+        </is>
+      </c>
       <c r="AX37" s="13"/>
       <c r="AY37" s="13" t="inlineStr">
         <is>
@@ -15707,17 +15597,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
-      <c r="BF37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
       <c r="BI37" s="23" t="inlineStr">
@@ -15727,34 +15609,34 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>4,6 Chilogrammi</t>
+          <t>6,2 Chilogrammi</t>
         </is>
       </c>
       <c r="BK37" s="23"/>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>36,5P x 29,4l x 38,1H cm</t>
+          <t>51,3P x 27,5l x 28,8H cm</t>
         </is>
       </c>
       <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>6.98 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>6.98 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>39.4 x 35.7 x 31.4 cm</t>
+          <t>54.8 x 37.1 x 30.8 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>39.40 x 35.70 x 31.40 cm</t>
+          <t>54.80 x 37.10 x 30.80 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -15770,11 +15652,15 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Marchio: LEHMANN | Colore: Nero/Rosso | Peso articolo: 4,7 Chilogrammi | Dimensioni del prodotto: 22P x 32l x 30H cm | Stile: Contemporaneo</t>
+        </is>
+      </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
           <t>LEHMANN</t>
@@ -15782,28 +15668,36 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN Prowash Lavatappeti Professionale, 2000 W, Lava Tappezzeria Potente con 2 Serbatoi - Acqua Pulita 3L e Sporca 1,5L, T</t>
-        </is>
-      </c>
-      <c r="I38" s="14"/>
+          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C, Pulitore Tappeti, Pulitore Divano, Lava e Aspira, Aspirazione 16 kPa</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>4 modalità di pulizia in un solo dispositivo: acqua fredda, acqua calda, vapore per tessuti e pulizia a vapore: Lehmann SteamWash combina le funzioni di lavatappezzeria, lavatappeti, pulitore tappeti, pulitore divano e pulitore a vapore in un unico apparecchio compatto. Puoi scegliere tra lavaggio con acqua fredda, acqua calda fino a circa 60°C, pulizia dei tessuti a vapore o pulizia a vapore ad alta temperatura fino a circa 116°C. Ideale per divani, tappeti, moquette, materassi, sedili auto e numerose superfici della casa
+Lava e aspira per una pulizia profonda di tappeti, divani e tappezzeria: Grazie alla combinazione di erogazione dell’acqua e aspirazione ≥16 kPa, SteamWash lava e aspira contemporaneamente, aiutando a rimuovere sporco, macchie e residui dai tessuti. Perfetto come pulitore tappezzeria, lavatessuti, lavamoquette e lavatappeti e divani per mantenere gli ambienti più puliti e freschi, soprattutto nelle case con bambini e animali domestici
+Pulitore a vapore con aspirazione per cucina, bagno, fughe e superfici difficili: Con una temperatura del vapore di circa 116°C, SteamWash funziona come pulitore a vapore con aspirazione, ideale per la pulizia a vapore di fughe, piastrelle, vetri, specchi, box doccia e rubinetterie. Un pratico aspirapolvere a vapore e steam cleaner per la pulizia quotidiana della casa senza utilizzare più dispositivi separati
+Ideale per la pulizia di divani, tappeti, materassi e interni auto: Utilizzabile come pulitore divano, pulitore tappeti, lavatappezzeria e lavatessuti, SteamWash aiuta a mantenere puliti divani, poltrone, tappeti, materassi e sedili auto. La combinazione di acqua, calore e aspirazione favorisce una pulizia più efficace delle superfici tessili più utilizzate
+Grandi serbatoi, accessori completi e funzione autopulente: Il serbatoio acqua pulita da 1,9 L e quello di recupero da 1,4 L consentono sessioni di pulizia più lunghe. Il tubo da 2,3 m, il cavo da 4 m e le ruote girevoli a 360° garantiscono libertà di movimento durante la pulizia casa. La funzione di autopulizia facilita la manutenzione del sistema dopo ogni utilizzo</t>
+        </is>
+      </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CLYF3DMZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -15813,17 +15707,17 @@
       </c>
       <c r="N38" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
         </is>
       </c>
       <c r="O38" s="15">
-        <v>66356</v>
+        <v>7978</v>
       </c>
       <c r="P38" s="15">
-        <v>-78489</v>
+        <v>11414</v>
       </c>
       <c r="Q38" s="16">
-        <v>-1.25</v>
+        <v>0.38</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -15832,17 +15726,17 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="U38" s="16">
-        <v>0.86</v>
+        <v>2.29</v>
       </c>
       <c r="V38" s="15">
-        <v>8059</v>
+        <v>7399</v>
       </c>
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
@@ -15850,41 +15744,41 @@
         <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>129.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA38" s="4"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>386</v>
+        <v>37</v>
       </c>
       <c r="AE38" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.1935</v>
+        <v>0.2027</v>
       </c>
       <c r="AH38" s="20">
-        <v>10.24</v>
+        <v>9.35</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>921</v>
+        <v>116</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -15903,7 +15797,7 @@
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU38" s="13" t="inlineStr">
@@ -15937,7 +15831,11 @@
       </c>
       <c r="BD38" s="13"/>
       <c r="BE38" s="13"/>
-      <c r="BF38" s="13"/>
+      <c r="BF38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
       <c r="BI38" s="23" t="inlineStr">
@@ -15947,34 +15845,34 @@
       </c>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>6,2 Chilogrammi</t>
+          <t>4,7 Chilogrammi</t>
         </is>
       </c>
       <c r="BK38" s="23"/>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>51,3P x 27,5l x 28,8H cm</t>
+          <t>22P x 32l x 30H cm</t>
         </is>
       </c>
       <c r="BM38" s="23"/>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>54.8 x 37.1 x 30.8 cm</t>
+          <t>37.3 x 35.7 x 31.8 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>54.80 x 37.10 x 30.80 cm</t>
+          <t>37.30 x 35.70 x 31.80 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
@@ -15990,52 +15888,52 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Marchio: LEHMANN | Colore: Nero/Rosso | Peso articolo: 4,7 Chilogrammi | Dimensioni del prodotto: 22P x 32l x 30H cm | Stile: Contemporaneo</t>
+          <t>Marchio: Hearten | Colore: Bianco | Peso articolo: 2,5 Chilogrammi | Dimensioni del prodotto: 23,2P x 29,9l x 17,3H cm | Capacità: 1,5 litri</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C, Pulitore Tappeti, Pulitore Divano, Lava e Aspira, Aspirazione 16 kPa</t>
+          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-Pulizia</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>4 modalità di pulizia in un solo dispositivo: acqua fredda, acqua calda, vapore per tessuti e pulizia a vapore: Lehmann SteamWash combina le funzioni di lavatappezzeria, lavatappeti, pulitore tappeti, pulitore divano e pulitore a vapore in un unico apparecchio compatto. Puoi scegliere tra lavaggio con acqua fredda, acqua calda fino a circa 60°C, pulizia dei tessuti a vapore o pulizia a vapore ad alta temperatura fino a circa 116°C. Ideale per divani, tappeti, moquette, materassi, sedili auto e numerose superfici della casa
-Lava e aspira per una pulizia profonda di tappeti, divani e tappezzeria: Grazie alla combinazione di erogazione dell’acqua e aspirazione ≥16 kPa, SteamWash lava e aspira contemporaneamente, aiutando a rimuovere sporco, macchie e residui dai tessuti. Perfetto come pulitore tappezzeria, lavatessuti, lavamoquette e lavatappeti e divani per mantenere gli ambienti più puliti e freschi, soprattutto nelle case con bambini e animali domestici
-Pulitore a vapore con aspirazione per cucina, bagno, fughe e superfici difficili: Con una temperatura del vapore di circa 116°C, SteamWash funziona come pulitore a vapore con aspirazione, ideale per la pulizia a vapore di fughe, piastrelle, vetri, specchi, box doccia e rubinetterie. Un pratico aspirapolvere a vapore e steam cleaner per la pulizia quotidiana della casa senza utilizzare più dispositivi separati
-Ideale per la pulizia di divani, tappeti, materassi e interni auto: Utilizzabile come pulitore divano, pulitore tappeti, lavatappezzeria e lavatessuti, SteamWash aiuta a mantenere puliti divani, poltrone, tappeti, materassi e sedili auto. La combinazione di acqua, calore e aspirazione favorisce una pulizia più efficace delle superfici tessili più utilizzate
-Grandi serbatoi, accessori completi e funzione autopulente: Il serbatoio acqua pulita da 1,9 L e quello di recupero da 1,4 L consentono sessioni di pulizia più lunghe. Il tubo da 2,3 m, il cavo da 4 m e le ruote girevoli a 360° garantiscono libertà di movimento durante la pulizia casa. La funzione di autopulizia facilita la manutenzione del sistema dopo ogni utilizzo</t>
+          <t>【Aspirazione potente】Pulitore tappezzeria è dotato di un motore ad alte prestazioni che genera una potenza di aspirazione di 22 kPa, capace di penetrare in profondità nelle fibre tessili per rimuovere facilmente polvere ostinata e macchie da tappeti, divani, materassi e sedili auto. Che si tratti di zuppe versate, bevande rovesciate o macchie di urina di animali, tutto viene aspirato in un attimo, senza lasciare traccia.
+【Autopulizia】Lavatessuti è provvisto di una funzione di autopulizia. Una volta terminata la pulizia, basta montare l'apposito accessorio per l'autopulizia e premere il pulsante: il dispositivo laverà automaticamente il tubo flessibile interno, evitando accumuli di sporco e cattivi odori. Nessuna smontaggio, nessun lavaggio manuale; la manutenzione quotidiana risulta semplice e veloce, e l'apparecchio rimane sempre in condizioni igieniche perfette.
+【Doppio serbatoio】Questo Pulitore tappeti è dotato di due serbatoi: 1,5 L per l'acqua pulita e 0,7 L per quella sporca. Con un pieno si puliscono ampie zone senza rabbocchi frequenti. È possibile aggiungere detergente specifico (da acquistare a parte) per tessuti nel serbatoio pulito per aumentare l'efficacia. I serbatoi separati impediscono contaminazioni. Inoltre, il dispositivo si arresta automaticamente quando il serbatoio sporco è pieno, evitando perdite e garantendo sicurezza.
+【Ampio raggio d'azione】Pulitore Divano è fornito di un cavo di alimentazione da 5 m e di un tubo flessibile da 1,4 m, per un raggio d'azione totale di 6,5 m. Ciò consente di pulire comodamente ampie zone, divani, poltrone o angoli senza dover cambiare continuamente presa di corrente. Con un peso di soli 2,5 kg e dimensioni compatte, è facile da trasportare e riporre.
+【Design di stoccaggio pratico】Pulitore divani include due spazzole: una standard per la pulizia quotidiana e una specifica per i peli di animali, che rimuove facilmente i peli incastrati nelle fibre. Sono inoltre presenti un supporto per il manico e un fermacavo per riporre ordinatamente il tutto, evitando grovigli e risparmiando spazio.</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16049,13 +15947,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>7978</v>
+        <v>15970</v>
       </c>
       <c r="P39" s="15">
-        <v>11414</v>
+        <v>989</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16064,55 +15962,59 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>74</v>
-      </c>
-      <c r="U39" s="16">
-        <v>2.29</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="U39" s="16"/>
       <c r="V39" s="15">
-        <v>7399</v>
-      </c>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
+        <v>7061</v>
+      </c>
+      <c r="W39" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X39" s="15">
+        <v>3549</v>
+      </c>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>99.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA39" s="4"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="AE39" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF39" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.2027</v>
+        <v>0.1308</v>
       </c>
       <c r="AH39" s="20">
-        <v>9.35</v>
+        <v>5.21</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -16130,7 +16032,7 @@
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Hearten Direct</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
@@ -16140,17 +16042,17 @@
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>Hong Kong 999077 HK</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
@@ -16167,7 +16069,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD39" s="13"/>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="13"/>
       <c r="BF39" s="13" t="inlineStr">
         <is>
@@ -16183,39 +16089,39 @@
       </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>4,7 Chilogrammi</t>
+          <t>2,5 Chilogrammi</t>
         </is>
       </c>
       <c r="BK39" s="23"/>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>22P x 32l x 30H cm</t>
+          <t>23,2P x 29,9l x 17,3H cm</t>
         </is>
       </c>
       <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>3.34 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>3.34 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>37.3 x 35.7 x 31.8 cm</t>
+          <t>32.4 x 32.2 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>37.30 x 35.70 x 31.80 cm</t>
+          <t>32.40 x 32.20 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16226,275 +16132,31 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0H7C5V7MZ</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Hearten | Colore: Bianco | Peso articolo: 2,5 Chilogrammi | Dimensioni del prodotto: 23,2P x 29,9l x 17,3H cm | Capacità: 1,5 litri</t>
+          <t>Marchio: VacniQ | Colore: Grigio | Capacità: 1,2 litri | Conteggio unità: 1.0 Conteggio | Produttore: VacniQ</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Hearten</t>
+          <t>VacniQ</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-Pulizia</t>
+          <t>C688 Aspirapolvere lavante 4 in 1, 25000 Pa, 1800 W. Riscaldamento, disinfezione, display LED e avvisi vocali. Ideale per divani, tappeti, sedili auto, materassi, cuscini animali</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>【Aspirazione potente】Pulitore tappezzeria è dotato di un motore ad alte prestazioni che genera una potenza di aspirazione di 22 kPa, capace di penetrare in profondità nelle fibre tessili per rimuovere facilmente polvere ostinata e macchie da tappeti, divani, materassi e sedili auto. Che si tratti di zuppe versate, bevande rovesciate o macchie di urina di animali, tutto viene aspirato in un attimo, senza lasciare traccia.
-【Autopulizia】Lavatessuti è provvisto di una funzione di autopulizia. Una volta terminata la pulizia, basta montare l'apposito accessorio per l'autopulizia e premere il pulsante: il dispositivo laverà automaticamente il tubo flessibile interno, evitando accumuli di sporco e cattivi odori. Nessuna smontaggio, nessun lavaggio manuale; la manutenzione quotidiana risulta semplice e veloce, e l'apparecchio rimane sempre in condizioni igieniche perfette.
-【Doppio serbatoio】Questo Pulitore tappeti è dotato di due serbatoi: 1,5 L per l'acqua pulita e 0,7 L per quella sporca. Con un pieno si puliscono ampie zone senza rabbocchi frequenti. È possibile aggiungere detergente specifico (da acquistare a parte) per tessuti nel serbatoio pulito per aumentare l'efficacia. I serbatoi separati impediscono contaminazioni. Inoltre, il dispositivo si arresta automaticamente quando il serbatoio sporco è pieno, evitando perdite e garantendo sicurezza.
-【Ampio raggio d'azione】Pulitore Divano è fornito di un cavo di alimentazione da 5 m e di un tubo flessibile da 1,4 m, per un raggio d'azione totale di 6,5 m. Ciò consente di pulire comodamente ampie zone, divani, poltrone o angoli senza dover cambiare continuamente presa di corrente. Con un peso di soli 2,5 kg e dimensioni compatte, è facile da trasportare e riporre.
-【Design di stoccaggio pratico】Pulitore divani include due spazzole: una standard per la pulizia quotidiana e una specifica per i peli di animali, che rimuove facilmente i peli incastrati nelle fibre. Sono inoltre presenti un supporto per il manico e un fermacavo per riporre ordinatamente il tutto, evitando grovigli e risparmiando spazio.</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
-        </is>
-      </c>
-      <c r="K40" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L40" s="14" t="inlineStr">
-        <is>
-          <t>B0H263J8GJ</t>
-        </is>
-      </c>
-      <c r="M40" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O40" s="15">
-        <v>15970</v>
-      </c>
-      <c r="P40" s="15">
-        <v>989</v>
-      </c>
-      <c r="Q40" s="16">
-        <v>0.08</v>
-      </c>
-      <c r="R40" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S40" s="18" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T40" s="15">
-        <v>107</v>
-      </c>
-      <c r="U40" s="16"/>
-      <c r="V40" s="15">
-        <v>7061</v>
-      </c>
-      <c r="W40" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X40" s="15">
-        <v>3549</v>
-      </c>
-      <c r="Y40" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>65.99</v>
-      </c>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE40" s="15">
-        <v>14</v>
-      </c>
-      <c r="AF40" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG40" s="22">
-        <v>0.1308</v>
-      </c>
-      <c r="AH40" s="20">
-        <v>5.21</v>
-      </c>
-      <c r="AI40" s="16">
-        <v>0.77</v>
-      </c>
-      <c r="AJ40"/>
-      <c r="AK40" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AL40" s="19">
-        <v>35</v>
-      </c>
-      <c r="AM40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN40" s="13"/>
-      <c r="AO40" s="13"/>
-      <c r="AP40" s="4"/>
-      <c r="AQ40" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR40" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS40" s="14" t="inlineStr">
-        <is>
-          <t>Hearten Direct</t>
-        </is>
-      </c>
-      <c r="AT40" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV40" s="14" t="inlineStr">
-        <is>
-          <t>Hong Kong 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
-        </is>
-      </c>
-      <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="13"/>
-      <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE40" s="13"/>
-      <c r="BF40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG40" s="13"/>
-      <c r="BH40" s="14"/>
-      <c r="BI40" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ40" s="23" t="inlineStr">
-        <is>
-          <t>2,5 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK40" s="23"/>
-      <c r="BL40" s="23" t="inlineStr">
-        <is>
-          <t>23,2P x 29,9l x 17,3H cm</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
-      <c r="BN40" s="23" t="inlineStr">
-        <is>
-          <t>3.34 kg</t>
-        </is>
-      </c>
-      <c r="BO40" s="23" t="inlineStr">
-        <is>
-          <t>3.34 kg</t>
-        </is>
-      </c>
-      <c r="BP40" s="23" t="inlineStr">
-        <is>
-          <t>32.4 x 32.2 x 19.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ40" s="23" t="inlineStr">
-        <is>
-          <t>32.40 x 32.20 x 19.40 cm</t>
-        </is>
-      </c>
-      <c r="BR40" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
-        <v>40</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>B0H7C5V7MZ</t>
-        </is>
-      </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: VacniQ | Colore: Grigio | Capacità: 1,2 litri | Conteggio unità: 1.0 Conteggio | Produttore: VacniQ</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>VacniQ</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>C688 Aspirapolvere lavante 4 in 1, 25000 Pa, 1800 W. Riscaldamento, disinfezione, display LED e avvisi vocali. Ideale per divani, tappeti, sedili auto, materassi, cuscini animali</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>Potente aspirazione: dotato di un motore ad alta potenza da 1800 W, con una forza di aspirazione fino a 25 kPa, rimuove facilmente lo sporco ostinato e le impurità residue dall’interno. Sia la polvere quotidiana che le macchie di bevande difficili da eliminare vengono pulite rapidamente, mantenendo efficacemente i tessuti puliti e belli.
 4 modalità di pulizia: dotato di quattro modalità di pulizia professionali (acqua fredda, acqua calda, vapore e sterilizzazione), soddisfa le esigenze di pulizia accurata in diversi contesti e su diversi materiali. Il corpo macchina è dotato di un display LED intelligente ad alta definizione che mostra chiaramente lo stato delle modalità, consentendo di passare da una all’altra con un solo tocco.
@@ -16505,19 +16167,229 @@
 Sistema di autopulizia: quando la modalità di autopulizia è attivata, il sistema rimuove lo sporco residuo all’interno dei tubi, prevenendo la formazione di cattivi odori; allo stesso tempo, garantisce un’esperienza d’uso più comoda e prolunga la durata del prodotto. (Prima di utilizzare la modalità di autopulizia, è necessario utilizzare il tubo di autopulizia).</t>
         </is>
       </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/dp/B0H7C5V7MZ?psc=1</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>B0H7C5V7MZ</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+        </is>
+      </c>
+      <c r="O40" s="15">
+        <v>16868</v>
+      </c>
+      <c r="P40" s="15">
+        <v>134944</v>
+      </c>
+      <c r="Q40" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>Lavatappeti</t>
+        </is>
+      </c>
+      <c r="S40" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T40" s="15">
+        <v>49</v>
+      </c>
+      <c r="U40" s="16"/>
+      <c r="V40" s="15">
+        <v>6860</v>
+      </c>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="20">
+        <v>139.99</v>
+      </c>
+      <c r="AA40" s="4"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="19">
+        <v>6</v>
+      </c>
+      <c r="AE40" s="15">
+        <v>4</v>
+      </c>
+      <c r="AF40" s="21">
+        <v>5</v>
+      </c>
+      <c r="AG40" s="22">
+        <v>0.0816</v>
+      </c>
+      <c r="AH40" s="20">
+        <v>5.49</v>
+      </c>
+      <c r="AI40" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="AJ40"/>
+      <c r="AK40" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AL40" s="19">
+        <v>86</v>
+      </c>
+      <c r="AM40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN40" s="13"/>
+      <c r="AO40" s="13"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS40" s="14" t="inlineStr">
+        <is>
+          <t>Guevel David Commerce</t>
+        </is>
+      </c>
+      <c r="AT40" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU40" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV40" s="14" t="inlineStr">
+        <is>
+          <t>Paris 75002 FR</t>
+        </is>
+      </c>
+      <c r="AW40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
+        </is>
+      </c>
+      <c r="AX40" s="13"/>
+      <c r="AY40" s="13"/>
+      <c r="AZ40" s="13"/>
+      <c r="BA40" s="13"/>
+      <c r="BB40" s="13"/>
+      <c r="BC40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD40" s="13"/>
+      <c r="BE40" s="13"/>
+      <c r="BF40" s="13"/>
+      <c r="BG40" s="13"/>
+      <c r="BH40" s="14"/>
+      <c r="BI40" s="23"/>
+      <c r="BJ40" s="23" t="inlineStr">
+        <is>
+          <t>6 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK40" s="23" t="inlineStr">
+        <is>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="23"/>
+      <c r="BM40" s="23"/>
+      <c r="BN40" s="23" t="inlineStr">
+        <is>
+          <t>6 kg</t>
+        </is>
+      </c>
+      <c r="BO40" s="23" t="inlineStr">
+        <is>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BP40" s="23" t="inlineStr">
+        <is>
+          <t>44 x 32 x 26 cm</t>
+        </is>
+      </c>
+      <c r="BQ40" s="23" t="inlineStr">
+        <is>
+          <t>44.00 x 32.00 x 26.00 cm</t>
+        </is>
+      </c>
+      <c r="BR40" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>B0BPZJSXCQ</t>
+        </is>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Cecotec</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+        </is>
+      </c>
+      <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H7C5V7MZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0H7C5V7MZ</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16527,17 +16399,17 @@
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O41" s="15">
-        <v>16868</v>
+        <v>38034</v>
       </c>
       <c r="P41" s="15">
-        <v>134944</v>
+        <v>10243</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.78</v>
+        <v>0.23</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16546,15 +16418,17 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>49</v>
-      </c>
-      <c r="U41" s="16"/>
+        <v>65</v>
+      </c>
+      <c r="U41" s="16">
+        <v>-0.17</v>
+      </c>
       <c r="V41" s="15">
-        <v>6860</v>
+        <v>5752</v>
       </c>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
@@ -16562,41 +16436,41 @@
         <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>139.99</v>
+        <v>70.43</v>
       </c>
       <c r="AA41" s="4"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>6</v>
+        <v>3297</v>
       </c>
       <c r="AE41" s="15">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AF41" s="21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.0816</v>
+        <v>0.5231</v>
       </c>
       <c r="AH41" s="20">
-        <v>5.49</v>
+        <v>8.9</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>86</v>
+        <v>1287</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16606,35 +16480,31 @@
         <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Guevel David Commerce</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV41" s="14" t="inlineStr">
-        <is>
-          <t>Paris 75002 FR</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
       <c r="AW41" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9</t>
         </is>
       </c>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16643,47 +16513,55 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13"/>
+      <c r="BD41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>6 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK41" s="23" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="23"/>
+          <t>3,6 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK41" s="23"/>
+      <c r="BL41" s="23" t="inlineStr">
+        <is>
+          <t>27,5P x 22l x 28,5H cm</t>
+        </is>
+      </c>
       <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>6 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>44 x 32 x 26 cm</t>
+          <t>35.2 x 31 x 30.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 32.00 x 26.00 cm</t>
+          <t>35.20 x 31.00 x 30.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16694,40 +16572,56 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
-        </is>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
+          <t>B0GFF7C519</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Set name: X5</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Marchio: Akitas | Colore: Rosso | Peso articolo: 2,5 Chilogrammi | Dimensioni del prodotto: 36P x 22l x 28H cm | Stile: Contemporaneo</t>
+        </is>
+      </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
-        </is>
-      </c>
-      <c r="I42" s="14"/>
+          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, leggero per macchie di animali su divani e auto</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Dotato di un potente motore da 400 W Offre un'aspirazione potente per affrontare diversi scenari di pulizia e rimuovere efficacemente anche le macchie piu ostinate.
+Include 30 ml di soluzione detergente starter Altamente concentrata con rapporto 1:25, a bassa schiuma e sicura per l'uso in macchina. E disponibile anche una bottiglia da 1 litro acquistabile separatamente.
+Sistema a doppio serbatoio Dotato di un serbatoio per acqua pulita da 0,8 L e di un serbatoio per acqua sporca da 0,7 L, per separare in modo efficiente acqua pulita e acqua sporca e garantire sessioni di pulizia igieniche e senza interruzioni.
+Pratico e compatto Con un tubo di aspirazione lungo 1,2 m e un cavo di alimentazione lungo 3 m, offre un'ottima portata da normali prese elettriche. Le dimensioni compatte di 25 x 13 x 25,5 cm ne facilitano la conservazione in piccoli spazi o armadi.
+Dotato di due accessori Include la spazzola manuale per macchie ostinate e l'accessorio per tappezzeria, per rispondere facilmente a diverse esigenze di pulizia.</t>
+        </is>
+      </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0HL8QF6Q8</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16737,17 +16631,17 @@
       </c>
       <c r="N42" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
         </is>
       </c>
       <c r="O42" s="15">
-        <v>38034</v>
+        <v>5174</v>
       </c>
       <c r="P42" s="15">
-        <v>10243</v>
+        <v>56561</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.23</v>
+        <v>0.9</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16756,59 +16650,65 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="U42" s="16">
-        <v>-0.17</v>
+        <v>0.19</v>
       </c>
       <c r="V42" s="15">
-        <v>5752</v>
-      </c>
-      <c r="W42" s="15"/>
-      <c r="X42" s="15"/>
+        <v>5745</v>
+      </c>
+      <c r="W42" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X42" s="15">
+        <v>3211</v>
+      </c>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="20">
-        <v>70.43</v>
+        <v>59.84</v>
       </c>
       <c r="AA42" s="4"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>3297</v>
+        <v>222</v>
       </c>
       <c r="AE42" s="15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.5231</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="20">
-        <v>8.9</v>
+        <v>5.43</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>1287</v>
+        <v>249</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
@@ -16818,23 +16718,31 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>Tin Hau Hong Kong 852 HK</t>
+        </is>
+      </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
@@ -16867,39 +16775,39 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>3,6 Chilogrammi</t>
+          <t>2,5 Chilogrammi</t>
         </is>
       </c>
       <c r="BK42" s="23"/>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>27,5P x 22l x 28,5H cm</t>
+          <t>36P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>3.2 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>35.2 x 31 x 30.5 cm</t>
+          <t>34.5 x 27.9 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>35.20 x 31.00 x 30.50 cm</t>
+          <t>34.50 x 27.90 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16910,281 +16818,35 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0H5L383SW</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Set name: X5</t>
+          <t>Set name: CM005</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Akitas | Colore: Rosso | Peso articolo: 2,5 Chilogrammi | Dimensioni del prodotto: 36P x 22l x 28H cm | Stile: Contemporaneo</t>
+          <t>Marchio: Livatro | Caratteristica speciale: Doppio serbatoio | Superfici consigliate: Tappeto | Componenti inclusi: Spazzola standard, spazzola angolare, spazzola in silicone, spazzola in nylon, spazzola in acciaio inox e bocchetta vapore | Peso articolo: 4,8 Chilogrammi</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0H5L383SW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, leggero per macchie di animali su divani e auto</t>
+          <t>Livatro Lavatappeti e Pulitore a Vapore 2100 W per Divani, Sofà e Auto</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>Dotato di un potente motore da 400 W Offre un'aspirazione potente per affrontare diversi scenari di pulizia e rimuovere efficacemente anche le macchie piu ostinate.
-Include 30 ml di soluzione detergente starter Altamente concentrata con rapporto 1:25, a bassa schiuma e sicura per l'uso in macchina. E disponibile anche una bottiglia da 1 litro acquistabile separatamente.
-Sistema a doppio serbatoio Dotato di un serbatoio per acqua pulita da 0,8 L e di un serbatoio per acqua sporca da 0,7 L, per separare in modo efficiente acqua pulita e acqua sporca e garantire sessioni di pulizia igieniche e senza interruzioni.
-Pratico e compatto Con un tubo di aspirazione lungo 1,2 m e un cavo di alimentazione lungo 3 m, offre un'ottima portata da normali prese elettriche. Le dimensioni compatte di 25 x 13 x 25,5 cm ne facilitano la conservazione in piccoli spazi o armadi.
-Dotato di due accessori Include la spazzola manuale per macchie ostinate e l'accessorio per tappezzeria, per rispondere facilmente a diverse esigenze di pulizia.</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
-        </is>
-      </c>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L43" s="14" t="inlineStr">
-        <is>
-          <t>B0HL8QF6Q8</t>
-        </is>
-      </c>
-      <c r="M43" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O43" s="15">
-        <v>5174</v>
-      </c>
-      <c r="P43" s="15">
-        <v>56561</v>
-      </c>
-      <c r="Q43" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="R43" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S43" s="18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="T43" s="15">
-        <v>96</v>
-      </c>
-      <c r="U43" s="16">
-        <v>0.19</v>
-      </c>
-      <c r="V43" s="15">
-        <v>5745</v>
-      </c>
-      <c r="W43" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X43" s="15">
-        <v>3211</v>
-      </c>
-      <c r="Y43" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z43" s="20">
-        <v>59.84</v>
-      </c>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="2"/>
-      <c r="AD43" s="19">
-        <v>222</v>
-      </c>
-      <c r="AE43" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG43" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="20">
-        <v>5.43</v>
-      </c>
-      <c r="AI43" s="16">
-        <v>0.76</v>
-      </c>
-      <c r="AJ43"/>
-      <c r="AK43" s="13" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="AL43" s="19">
-        <v>249</v>
-      </c>
-      <c r="AM43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN43" s="13"/>
-      <c r="AO43" s="13"/>
-      <c r="AP43" s="4"/>
-      <c r="AQ43" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR43" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="14" t="inlineStr">
-        <is>
-          <t>Chelsea Company Limited</t>
-        </is>
-      </c>
-      <c r="AT43" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU43" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV43" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
-      <c r="AW43" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
-        </is>
-      </c>
-      <c r="AX43" s="13"/>
-      <c r="AY43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ43" s="13"/>
-      <c r="BA43" s="13"/>
-      <c r="BB43" s="13"/>
-      <c r="BC43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE43" s="13"/>
-      <c r="BF43" s="13"/>
-      <c r="BG43" s="13"/>
-      <c r="BH43" s="14"/>
-      <c r="BI43" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ43" s="23" t="inlineStr">
-        <is>
-          <t>2,5 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK43" s="23"/>
-      <c r="BL43" s="23" t="inlineStr">
-        <is>
-          <t>36P x 22l x 28H cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
-      <c r="BN43" s="23" t="inlineStr">
-        <is>
-          <t>3.2 kg</t>
-        </is>
-      </c>
-      <c r="BO43" s="23" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
-      <c r="BP43" s="23" t="inlineStr">
-        <is>
-          <t>34.5 x 27.9 x 19.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="23" t="inlineStr">
-        <is>
-          <t>34.50 x 27.90 x 19.40 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
-        <v>43</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>B0H5L383SW</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>Set name: CM005</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Livatro | Caratteristica speciale: Doppio serbatoio | Superfici consigliate: Tappeto | Componenti inclusi: Spazzola standard, spazzola angolare, spazzola in silicone, spazzola in nylon, spazzola in acciaio inox e bocchetta vapore | Peso articolo: 4,8 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>Livatro</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0H5L383SW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>Livatro Lavatappeti e Pulitore a Vapore 2100 W per Divani, Sofà e Auto</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
         <is>
           <t>Vapore ad Alta Temperatura 100°C per Pulizia Profonda e Igienizzante: Il lavatappeti e divani lava e asciuga è dotato di un sistema di riscaldamento rapido da 2100 W, che raggiunge i 60°C in soli 15 secondi ed eroga vapore a 100°C in 30 secondi. Il vapore ad alta pressione penetra in profondità nelle fibre, e il lavatappeti ammorbidisce e scioglie rapidamente macchie di olio indurito, residui zuccherini, urina di animali e altro. L'alta temperatura aiuta a ridurre batteri e acari, minimizzando gli odori per creare un ambiente domestico igienizzato e salutare.
 ASPIRAZIONE 18 KPA PER UNA PULIZIA PROFONDA: Il lavatappeti aiuta a sciogliere lo sporco utilizzando acqua, acqua calda o vapore, aspirando successivamente residui e umidità in eccesso. Come lavadivani, aspiraliquidi e pulitore per tappeti, è adatto per divani, tappeti, materassi, sedili auto e altre superfici tessili idonee.
@@ -17193,19 +16855,223 @@
 6 ACCESSORI E AUTOPULIZIA DEL TUBO: Spazzola standard, spazzola angolare, spazzola in silicone, spazzola in nylon, spazzola in acciaio inox e bocchetta vapore consentono di affrontare diverse esigenze di pulizia. Dopo l’uso, l’accessorio autopulente permette di risciacquare il tubo; serbatoi e spazzole rimovibili facilitano inoltre la manutenzione regolare dell’apparecchio.</t>
         </is>
       </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/dp/B0H5L383SW?psc=1</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41ANJVSlEDL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr">
+        <is>
+          <t>B0HKHXC5FN</t>
+        </is>
+      </c>
+      <c r="M43" s="14" t="inlineStr">
+        <is>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+        </is>
+      </c>
+      <c r="O43" s="15">
+        <v>8874</v>
+      </c>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="16">
+        <v>0</v>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>Lavatappeti</t>
+        </is>
+      </c>
+      <c r="S43" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="T43" s="15">
+        <v>14</v>
+      </c>
+      <c r="U43" s="16"/>
+      <c r="V43" s="15">
+        <v>2800</v>
+      </c>
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
+      <c r="Y43" s="19">
+        <v>2</v>
+      </c>
+      <c r="Z43" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="AA43" s="4"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="21">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="20">
+        <v>8.9</v>
+      </c>
+      <c r="AI43" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="AJ43"/>
+      <c r="AK43" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AL43" s="19">
+        <v>21</v>
+      </c>
+      <c r="AM43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN43" s="13"/>
+      <c r="AO43" s="13"/>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR43" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS43" s="14" t="inlineStr">
+        <is>
+          <t>Yeaday</t>
+        </is>
+      </c>
+      <c r="AT43" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU43" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV43" s="14" t="inlineStr">
+        <is>
+          <t>NT 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A12SSLVAJYF874</t>
+        </is>
+      </c>
+      <c r="AX43" s="13"/>
+      <c r="AY43" s="13"/>
+      <c r="AZ43" s="13"/>
+      <c r="BA43" s="13"/>
+      <c r="BB43" s="13"/>
+      <c r="BC43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD43" s="13"/>
+      <c r="BE43" s="13"/>
+      <c r="BF43" s="13"/>
+      <c r="BG43" s="13"/>
+      <c r="BH43" s="14"/>
+      <c r="BI43" s="23"/>
+      <c r="BJ43" s="23" t="inlineStr">
+        <is>
+          <t>4,8 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK43" s="23"/>
+      <c r="BL43" s="23"/>
+      <c r="BM43" s="23"/>
+      <c r="BN43" s="23" t="inlineStr">
+        <is>
+          <t>4.77 kg</t>
+        </is>
+      </c>
+      <c r="BO43" s="23" t="inlineStr">
+        <is>
+          <t>4.77 kg</t>
+        </is>
+      </c>
+      <c r="BP43" s="23" t="inlineStr">
+        <is>
+          <t>37 x 35.6 x 22.9 cm</t>
+        </is>
+      </c>
+      <c r="BQ43" s="23" t="inlineStr">
+        <is>
+          <t>37.00 x 35.60 x 22.90 cm</t>
+        </is>
+      </c>
+      <c r="BR43" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13">
+        <v>43</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>B0BY2ZPQ1N</t>
+        </is>
+      </c>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Bissell</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0BY2ZPQ1N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>BISSELL Naturale detergente per pulizia profonda della moquette, 1,75 L, rimuove lo sporco ostinato degli animali domestici,</t>
+        </is>
+      </c>
+      <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H5L383SW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ANJVSlEDL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0HKHXC5FN</t>
+          <t>B0BY2ZPQ1N</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17215,15 +17081,17 @@
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O44" s="15">
-        <v>8874</v>
-      </c>
-      <c r="P44" s="15"/>
+        <v>32060</v>
+      </c>
+      <c r="P44" s="15">
+        <v>-5011</v>
+      </c>
       <c r="Q44" s="16">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17232,140 +17100,150 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>14</v>
-      </c>
-      <c r="U44" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="U44" s="16">
+        <v>-0.12</v>
+      </c>
       <c r="V44" s="15">
-        <v>2800</v>
-      </c>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
+        <v>1599</v>
+      </c>
+      <c r="W44" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X44" s="15">
+        <v>1000</v>
+      </c>
       <c r="Y44" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>199.99</v>
+        <v>19.99</v>
       </c>
       <c r="AA44" s="4"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="AE44" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF44" s="21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG44" s="22">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AH44" s="20">
-        <v>8.9</v>
+        <v>5.22</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.81</v>
+        <v>0.59</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>21</v>
+        <v>1247</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44" s="4"/>
-      <c r="AQ44" s="19">
-        <v>9</v>
-      </c>
+      <c r="AQ44" s="19"/>
       <c r="AR44" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Yeaday</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>NT 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A12SSLVAJYF874</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13"/>
+      <c r="AY44" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="13"/>
       <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23"/>
+      <c r="BI44" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>4,8 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK44" s="23"/>
-      <c r="BL44" s="23"/>
-      <c r="BM44" s="23"/>
+          <t>1.6 kg</t>
+        </is>
+      </c>
+      <c r="BK44" s="23" t="inlineStr">
+        <is>
+          <t>1.60 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="23" t="inlineStr">
+        <is>
+          <t>8.5 x 15.3 x 27.1 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>8.50 x 15.30 x 27.10 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>1.64 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>1.64 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>37 x 35.6 x 22.9 cm</t>
+          <t>27.1 x 15.3 x 8.5 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>37.00 x 35.60 x 22.90 cm</t>
+          <t>27.10 x 15.30 x 8.50 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -17376,48 +17254,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>STANHOME | Detergente Smacchiante Tappeti Carpet Cleaner, 500 ML, Pulisce e Smacchia i Tessuti d'Arredamento</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>DETERGENTE SMACCHIANTE: Prodotto specifico per la pulizia di tappeti, moquette e tessuti d'arredamento.
-SCHIUMA ATTIVA: Formula a doppia azione per una pulizia profonda e efficace delle macchie.
-PROFUMO FRESCO: Lascia un profumo gradevole dopo l'uso, migliorando l'ambiente domestico.
-MATERIALI RISPETTOSI: Composto da oltre il 78% di ingredienti naturali e imballaggio riciclabile.
-STANHOME: Offre soluzioni per prendersi cura di te e della tua casa. Ci impegniamo per la società e innoviamo per limitare l’impatto sull’ambiente.</t>
-        </is>
-      </c>
+          <t>Akitas Detergente per Tappeti 1L Schiuma Ridotta Profumo Floreale Per Divani Moquette Auto Compatibile con Lavamoquette Rimuo</t>
+        </is>
+      </c>
+      <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B086Q46MMD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DX2J6DW2?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61sF4ZQ-2cL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17427,17 +17297,17 @@
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O45" s="15">
-        <v>7336</v>
+        <v>65127</v>
       </c>
       <c r="P45" s="15">
-        <v>-1870</v>
+        <v>-46908</v>
       </c>
       <c r="Q45" s="16">
-        <v>-0.2</v>
+        <v>-1.04</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17446,99 +17316,93 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="U45" s="16">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="V45" s="15">
-        <v>2175</v>
-      </c>
-      <c r="W45" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X45" s="15">
-        <v>750</v>
-      </c>
+        <v>1599</v>
+      </c>
+      <c r="W45" s="15"/>
+      <c r="X45" s="15"/>
       <c r="Y45" s="19">
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>15</v>
+        <v>19.99</v>
       </c>
       <c r="AA45" s="4"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="AE45" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>3.74</v>
+        <v>5.19</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>2333</v>
+        <v>431</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45" s="4"/>
       <c r="AQ45" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>ITALIA 25038 IT</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
@@ -17550,7 +17414,11 @@
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
-      <c r="BC45" s="13"/>
+      <c r="BC45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
@@ -17563,47 +17431,39 @@
       </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>550 grammi</t>
-        </is>
-      </c>
-      <c r="BK45" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
+          <t>1,1 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK45" s="23"/>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>6,7 x 24 x 6,7 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="23" t="inlineStr">
-        <is>
-          <t>6.70 x 24.00 x 6.70 cm</t>
-        </is>
-      </c>
+          <t>36P x 22l x 28H cm</t>
+        </is>
+      </c>
+      <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>1.12 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>23.7 x 6.1 x 6 cm</t>
+          <t>24 x 8.3 x 7.7 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>23.70 x 6.10 x 6.00 cm</t>
+          <t>24.00 x 8.30 x 7.70 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>超大号信封</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -17614,40 +17474,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0BY2ZPQ1N</t>
+          <t>B0FN7HZHWY</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>Livatro</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0BY2ZPQ1N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Naturale detergente per pulizia profonda della moquette, 1,75 L, rimuove lo sporco ostinato degli animali domestici,</t>
+          <t>Livatro Detergente per Lavatappeti, Concentrato 1:30, Bassa Schiuma, 500 mlsDiluizione 1:30, 1 parte di prodotto con 30 par</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN7HZHWY?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0BY2ZPQ1N</t>
+          <t>B0FN7HZHWY</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17661,13 +17521,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>32060</v>
+        <v>42088</v>
       </c>
       <c r="P46" s="15">
-        <v>-5011</v>
+        <v>-11876</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.19</v>
+        <v>-0.39</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17676,145 +17536,149 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="U46" s="16">
-        <v>-0.12</v>
+        <v>-0.23</v>
       </c>
       <c r="V46" s="15">
-        <v>1599</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>1000</v>
-      </c>
+        <v>951</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>19.99</v>
+        <v>13.99</v>
       </c>
       <c r="AA46" s="4"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="AE46" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.05</v>
+        <v>0.0294</v>
       </c>
       <c r="AH46" s="20">
-        <v>5.22</v>
+        <v>5.12</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2023-04-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>1247</v>
+        <v>292</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46" s="4"/>
-      <c r="AQ46" s="19"/>
+      <c r="AQ46" s="19">
+        <v>10</v>
+      </c>
       <c r="AR46" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>HOORAY Group</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>HK 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13"/>
+      <c r="BC46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>1.6 kg</t>
+          <t>600 g</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.60 kg</t>
+          <t>600.00 g</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>8.5 x 15.3 x 27.1 cm</t>
+          <t>20 x 9,3 x 6,5 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>8.50 x 15.30 x 27.10 cm</t>
+          <t>20.00 x 9.30 x 6.50 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>1.64 kg</t>
+          <t>630 g</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.64 kg</t>
+          <t>630.00 g</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>27.1 x 15.3 x 8.5 cm</t>
+          <t>20 x 9.3 x 6.5 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>27.10 x 15.30 x 8.50 cm</t>
+          <t>20.00 x 9.30 x 6.50 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -17830,40 +17694,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0DX2J6DW2</t>
+          <t>B0FL7J1HCH</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Akitas Detergente per Tappeti 1L Schiuma Ridotta Profumo Floreale Per Divani Moquette Auto Compatibile con Lavamoquette Rimuo</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DX2J6DW2?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FL7J1HCH?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41y3sCvjPcL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0DX2J6DW2</t>
+          <t>B0FL7J1HCH</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -17873,17 +17737,15 @@
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
+          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
         </is>
       </c>
       <c r="O47" s="15">
-        <v>65127</v>
-      </c>
-      <c r="P47" s="15">
-        <v>-46908</v>
-      </c>
+        <v>40402</v>
+      </c>
+      <c r="P47" s="15"/>
       <c r="Q47" s="16">
-        <v>-1.04</v>
+        <v>0</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -17892,101 +17754,83 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>80</v>
-      </c>
-      <c r="U47" s="16">
-        <v>0.19</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U47" s="16"/>
       <c r="V47" s="15">
-        <v>1599</v>
+        <v>210</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>19.99</v>
+        <v>69.9</v>
       </c>
       <c r="AA47" s="4"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="AE47" s="15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
       </c>
-      <c r="AH47" s="20">
-        <v>5.19</v>
-      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47" s="4"/>
-      <c r="AQ47" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ47" s="19"/>
       <c r="AR47" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>Cecotec Italy</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
@@ -18000,48 +17844,24 @@
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>1,1 Chilogrammi</t>
+          <t>3,62 Chilogrammi</t>
         </is>
       </c>
       <c r="BK47" s="23"/>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>36P x 22l x 28H cm</t>
+          <t>27,5P x 22l x 28,5H cm</t>
         </is>
       </c>
       <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>1.12 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>1.12 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>24 x 8.3 x 7.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>24.00 x 8.30 x 7.70 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -18050,40 +17870,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Livatro</t>
+          <t>ICARE</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Livatro Detergente per Lavatappeti, Concentrato 1:30, Bassa Schiuma, 500 mlsDiluizione 1:30, 1 parte di prodotto con 30 par</t>
+          <t>ICARE 600W Lavatappeti Portatile - lavatappeti - 1,5L lava tappezzeria ad Acqua - Lava, Asciuga e Aspira 3 in 1 - Ideale per</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN7HZHWY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G8ZCQP4L?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71VDmFvdOXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0FN7HZHWY</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18097,13 +17917,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>42088</v>
+        <v>98358</v>
       </c>
       <c r="P48" s="15">
-        <v>-11876</v>
+        <v>495840</v>
       </c>
       <c r="Q48" s="16">
-        <v>-0.39</v>
+        <v>0.83</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18112,17 +17932,15 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>68</v>
-      </c>
-      <c r="U48" s="16">
-        <v>-0.23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>951</v>
+        <v>80</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -18130,37 +17948,37 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>13.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE48" s="15">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AF48" s="21">
         <v>4.2</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0294</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>5.12</v>
+        <v>8.9</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -18174,11 +17992,11 @@
         <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>HOORAY Group</t>
+          <t>VIVARALimited</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
@@ -18188,17 +18006,17 @@
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>HK 999077 HK</t>
+          <t>DUBLIN D01 KF30 IE</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -18211,7 +18029,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="13"/>
+      <c r="BD48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
@@ -18219,47 +18041,47 @@
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>600 g</t>
+          <t>5,33 Kilograms</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>600.00 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>20 x 9,3 x 6,5 cm</t>
+          <t>39 x 19.5 x 34 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
+          <t>39.00 x 19.50 x 34.00 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>630 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>630.00 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>20 x 9.3 x 6.5 cm</t>
+          <t>39.1 x 39 x 20.3 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 9.30 x 6.50 cm</t>
+          <t>39.10 x 39.00 x 20.30 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18270,40 +18092,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FL7J1HCH</t>
+          <t>B0H9PTVK8F</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>PUREBEAR Aspirapolvere per tappezzeria, 500 WsAspirazione di 18 kPa, compatto per pulizia a secco e bagnato, per tappeti, d</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FL7J1HCH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H9PTVK8F?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41y3sCvjPcL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FL7J1HCH</t>
+          <t>B0H9PTVK8F</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18311,54 +18133,34 @@
           <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
         </is>
       </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>40402</v>
-      </c>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-      <c r="Q49" s="16">
-        <v>0</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>3</v>
-      </c>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
       <c r="U49" s="16"/>
-      <c r="V49" s="15">
-        <v>210</v>
-      </c>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
       <c r="Y49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>69.9</v>
+        <v>139.99</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="AE49" s="15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
@@ -18370,15 +18172,15 @@
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>444</v>
+        <v>6</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN49" s="13"/>
@@ -18386,23 +18188,23 @@
       <c r="AP49" s="4"/>
       <c r="AQ49" s="19"/>
       <c r="AR49" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Italy</t>
+          <t>MengfanchaoMLw</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU49" s="13"/>
       <c r="AV49" s="14"/>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -18423,399 +18225,21 @@
       <c r="BI49" s="23"/>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>3,62 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK49" s="23"/>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>27,5P x 22l x 28,5H cm</t>
-        </is>
-      </c>
+          <t>4,39 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK49" s="23" t="inlineStr">
+        <is>
+          <t>4.39 kg</t>
+        </is>
+      </c>
+      <c r="BL49" s="23"/>
       <c r="BM49" s="23"/>
       <c r="BN49" s="23"/>
       <c r="BO49" s="23"/>
       <c r="BP49" s="23"/>
       <c r="BQ49" s="23"/>
       <c r="BR49" s="13"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0G8ZCQP4L</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>ICARE</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>ICARE 600W Lavatappeti Portatile - lavatappeti - 1,5L lava tappezzeria ad Acqua - Lava, Asciuga e Aspira 3 in 1 - Ideale per</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0G8ZCQP4L?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71VDmFvdOXL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0G8ZCQP4L</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>98358</v>
-      </c>
-      <c r="P50" s="15">
-        <v>495840</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.83</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>1</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>80</v>
-      </c>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>79.99</v>
-      </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>25</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>18</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.2</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>8.9</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.74</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>150</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>VIVARALimited</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>DUBLIN D01 KF30 IE</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>5,33 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>39 x 19.5 x 34 cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>39.00 x 19.50 x 34.00 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>39.1 x 39 x 20.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>39.10 x 39.00 x 20.30 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H9PTVK8F</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR Aspirapolvere per tappezzeria, 500 WsAspirazione di 18 kPa, compatto per pulizia a secco e bagnato, per tappeti, d</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H9PTVK8F?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H9PTVK8F</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>139.99</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>6</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>MengfanchaoMLw</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>4,39 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>4.39 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19048,161 +18472,146 @@
     <hyperlink ref="M32" r:id="rId225" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N32" r:id="rId226"/>
     <hyperlink ref="AW32" r:id="rId227" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.it/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K33" r:id="rId231" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/31BhvLWbbNL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.it/dp/B0DJWC9K1G"/>
+    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.it/dp/B0GM1PQ8M8"/>
+    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.it/stores/Rowenta/page/2FFCA3F5-1E5B-4BD9-BDC6-F0C2B3DB287C?lp_asin=B0GM1PQ8M8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.it/dp/B0GM1PQ8M8?psc=1"/>
+    <hyperlink ref="K33" r:id="rId231" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41bb8efrOAL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.it/dp/B0HCWGMQKH"/>
     <hyperlink ref="M33" r:id="rId233" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N33" r:id="rId234"/>
-    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.it/dp/B0GM1PQ8M8"/>
-    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.it/stores/Rowenta/page/2FFCA3F5-1E5B-4BD9-BDC6-F0C2B3DB287C?lp_asin=B0GM1PQ8M8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.it/dp/B0GM1PQ8M8?psc=1"/>
-    <hyperlink ref="K34" r:id="rId238" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/41bb8efrOAL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.it/dp/B0HCWGMQKH"/>
-    <hyperlink ref="M34" r:id="rId240" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N34" r:id="rId241"/>
-    <hyperlink ref="AW34" r:id="rId242" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KISR7QA7WRPG"/>
-    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K35" r:id="rId246" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N35" r:id="rId249"/>
-    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
-    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0CXMC73YV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.it/dp/B0CXMC73YV?psc=1"/>
-    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/I/41yDeV+UoOL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.it/dp/B0H63GF4QX"/>
+    <hyperlink ref="AW33" r:id="rId235" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KISR7QA7WRPG"/>
+    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K34" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="M34" r:id="rId241" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N34" r:id="rId242"/>
+    <hyperlink ref="AW34" r:id="rId243" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C35" r:id="rId244" tooltip="https://www.amazon.it/dp/B0CXMC73YV"/>
+    <hyperlink ref="G35" r:id="rId245" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0CXMC73YV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId246" tooltip="https://www.amazon.it/dp/B0CXMC73YV?psc=1"/>
+    <hyperlink ref="K35" r:id="rId247" tooltip="https://m.media-amazon.com/images/I/41yDeV+UoOL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId248" tooltip="https://www.amazon.it/dp/B0H63GF4QX"/>
+    <hyperlink ref="M35" r:id="rId249" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N35" r:id="rId250"/>
+    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
+    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.it/dp/B0DT7CPRW2?psc=1"/>
+    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.it/dp/B0H6JYXV4D"/>
     <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N36" r:id="rId257"/>
-    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
-    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.it/dp/B0DT7CPRW2?psc=1"/>
-    <hyperlink ref="K37" r:id="rId261" tooltip="https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.it/dp/B0H6JYXV4D"/>
+    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ?psc=1"/>
+    <hyperlink ref="K37" r:id="rId261" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
     <hyperlink ref="M37" r:id="rId263" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N37" r:id="rId264"/>
-    <hyperlink ref="C38" r:id="rId265" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="G38" r:id="rId266" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId267" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ?psc=1"/>
-    <hyperlink ref="K38" r:id="rId268" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId269" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="M38" r:id="rId270" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N38" r:id="rId271"/>
-    <hyperlink ref="AW38" r:id="rId272" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C39" r:id="rId273" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
-    <hyperlink ref="G39" r:id="rId274" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J39" r:id="rId275" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K39" r:id="rId276" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId277" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
-    <hyperlink ref="M39" r:id="rId278" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N39" r:id="rId279"/>
-    <hyperlink ref="AW39" r:id="rId280" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
-    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K40" r:id="rId284" tooltip="https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
-    <hyperlink ref="M40" r:id="rId286" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N40" r:id="rId287"/>
-    <hyperlink ref="AW40" r:id="rId288" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
-    <hyperlink ref="C41" r:id="rId289" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="G41" r:id="rId290" tooltip="https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId291" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ?psc=1"/>
-    <hyperlink ref="K41" r:id="rId292" tooltip="https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId293" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="M41" r:id="rId294" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N41" r:id="rId295"/>
-    <hyperlink ref="AW41" r:id="rId296" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
-    <hyperlink ref="C42" r:id="rId297" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="G42" r:id="rId298" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J42" r:id="rId299" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
-    <hyperlink ref="K42" r:id="rId300" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId301" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="M42" r:id="rId302" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N42" r:id="rId303"/>
-    <hyperlink ref="AW42" r:id="rId304" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9"/>
-    <hyperlink ref="C43" r:id="rId305" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="G43" r:id="rId306" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId307" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K43" r:id="rId308" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId309" tooltip="https://www.amazon.it/dp/B0HL8QF6Q8"/>
-    <hyperlink ref="M43" r:id="rId310" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N43" r:id="rId311"/>
-    <hyperlink ref="AW43" r:id="rId312" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C44" r:id="rId313" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
-    <hyperlink ref="G44" r:id="rId314" tooltip="https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0H5L383SW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId315" tooltip="https://www.amazon.it/dp/B0H5L383SW?psc=1"/>
-    <hyperlink ref="K44" r:id="rId316" tooltip="https://m.media-amazon.com/images/I/41ANJVSlEDL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId317" tooltip="https://www.amazon.it/dp/B0HKHXC5FN"/>
-    <hyperlink ref="M44" r:id="rId318" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N44" r:id="rId319"/>
-    <hyperlink ref="AW44" r:id="rId320" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A12SSLVAJYF874"/>
-    <hyperlink ref="C45" r:id="rId321" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="G45" r:id="rId322" tooltip="https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId323" tooltip="https://www.amazon.it/dp/B086Q46MMD?psc=1"/>
-    <hyperlink ref="K45" r:id="rId324" tooltip="https://images-na.ssl-images-amazon.com/images/I/61sF4ZQ-2cL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId325" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
+    <hyperlink ref="AW37" r:id="rId265" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C38" r:id="rId266" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="G38" r:id="rId267" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J38" r:id="rId268" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K38" r:id="rId269" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId270" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="M38" r:id="rId271" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N38" r:id="rId272"/>
+    <hyperlink ref="AW38" r:id="rId273" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
+    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/71o7iwPzixL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
+    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N39" r:id="rId280"/>
+    <hyperlink ref="AW39" r:id="rId281" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
+    <hyperlink ref="C40" r:id="rId282" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
+    <hyperlink ref="G40" r:id="rId283" tooltip="https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId284" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ?psc=1"/>
+    <hyperlink ref="K40" r:id="rId285" tooltip="https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId286" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
+    <hyperlink ref="M40" r:id="rId287" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N40" r:id="rId288"/>
+    <hyperlink ref="AW40" r:id="rId289" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
+    <hyperlink ref="C41" r:id="rId290" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="G41" r:id="rId291" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J41" r:id="rId292" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
+    <hyperlink ref="K41" r:id="rId293" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId294" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="M41" r:id="rId295" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N41" r:id="rId296"/>
+    <hyperlink ref="AW41" r:id="rId297" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9"/>
+    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K42" r:id="rId301" tooltip="https://images-na.ssl-images-amazon.com/images/I/71gcBr0vgXL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.it/dp/B0HL8QF6Q8"/>
+    <hyperlink ref="M42" r:id="rId303" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N42" r:id="rId304"/>
+    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.it/dp/B0H5L383SW"/>
+    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0H5L383SW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.it/dp/B0H5L383SW?psc=1"/>
+    <hyperlink ref="K43" r:id="rId309" tooltip="https://m.media-amazon.com/images/I/41ANJVSlEDL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.it/dp/B0HKHXC5FN"/>
+    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N43" r:id="rId312"/>
+    <hyperlink ref="AW43" r:id="rId313" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A12SSLVAJYF874"/>
+    <hyperlink ref="C44" r:id="rId314" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
+    <hyperlink ref="G44" r:id="rId315" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0BY2ZPQ1N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId316" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1"/>
+    <hyperlink ref="K44" r:id="rId317" tooltip="https://images-na.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId318" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
+    <hyperlink ref="M44" r:id="rId319" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N44" r:id="rId320"/>
+    <hyperlink ref="C45" r:id="rId321" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
+    <hyperlink ref="G45" r:id="rId322" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId323" tooltip="https://www.amazon.it/dp/B0DX2J6DW2?psc=1"/>
+    <hyperlink ref="K45" r:id="rId324" tooltip="https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId325" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
     <hyperlink ref="M45" r:id="rId326" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N45" r:id="rId327"/>
-    <hyperlink ref="AW45" r:id="rId328" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF"/>
-    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
-    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0BY2ZPQ1N&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N?psc=1"/>
-    <hyperlink ref="K46" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/610Ox3VdFHL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.it/dp/B0BY2ZPQ1N"/>
+    <hyperlink ref="AW45" r:id="rId328" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.it/dp/B0FN7HZHWY"/>
+    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.it/dp/B0FN7HZHWY?psc=1"/>
+    <hyperlink ref="K46" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.it/dp/B0FN7HZHWY"/>
     <hyperlink ref="M46" r:id="rId334" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N46" r:id="rId335"/>
-    <hyperlink ref="C47" r:id="rId336" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
-    <hyperlink ref="G47" r:id="rId337" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId338" tooltip="https://www.amazon.it/dp/B0DX2J6DW2?psc=1"/>
-    <hyperlink ref="K47" r:id="rId339" tooltip="https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId340" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
-    <hyperlink ref="M47" r:id="rId341" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N47" r:id="rId342"/>
-    <hyperlink ref="AW47" r:id="rId343" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C48" r:id="rId344" tooltip="https://www.amazon.it/dp/B0FN7HZHWY"/>
-    <hyperlink ref="G48" r:id="rId345" tooltip="https://www.amazon.it/stores/Livatro/page/6F7A6DCD-5AA5-4DBE-9647-CB399DC81AF2?lp_asin=B0FN7HZHWY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId346" tooltip="https://www.amazon.it/dp/B0FN7HZHWY?psc=1"/>
-    <hyperlink ref="K48" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/612q85DMSjL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId348" tooltip="https://www.amazon.it/dp/B0FN7HZHWY"/>
-    <hyperlink ref="M48" r:id="rId349" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N48" r:id="rId350"/>
-    <hyperlink ref="AW48" r:id="rId351" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
-    <hyperlink ref="C49" r:id="rId352" tooltip="https://www.amazon.it/dp/B0FL7J1HCH"/>
-    <hyperlink ref="G49" r:id="rId353" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J49" r:id="rId354" tooltip="https://www.amazon.it/dp/B0FL7J1HCH?psc=1"/>
-    <hyperlink ref="K49" r:id="rId355" tooltip="https://m.media-amazon.com/images/I/41y3sCvjPcL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId356" tooltip="https://www.amazon.it/dp/B0FL7J1HCH"/>
-    <hyperlink ref="M49" r:id="rId357" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N49" r:id="rId358"/>
-    <hyperlink ref="AW49" r:id="rId359" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9"/>
-    <hyperlink ref="C50" r:id="rId360" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="G50" r:id="rId361" tooltip="https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId362" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L?psc=1"/>
-    <hyperlink ref="K50" r:id="rId363" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VDmFvdOXL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId364" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="M50" r:id="rId365" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N50" r:id="rId366"/>
-    <hyperlink ref="AW50" r:id="rId367" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
-    <hyperlink ref="C51" r:id="rId368" tooltip="https://www.amazon.it/dp/B0H9PTVK8F"/>
-    <hyperlink ref="G51" r:id="rId369" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId370" tooltip="https://www.amazon.it/dp/B0H9PTVK8F?psc=1"/>
-    <hyperlink ref="K51" r:id="rId371" tooltip="https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId372" tooltip="https://www.amazon.it/dp/B0H9PTVK8F"/>
-    <hyperlink ref="M51" r:id="rId373" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="AW51" r:id="rId374" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
+    <hyperlink ref="AW46" r:id="rId336" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RZYXTJEAXRDS"/>
+    <hyperlink ref="C47" r:id="rId337" tooltip="https://www.amazon.it/dp/B0FL7J1HCH"/>
+    <hyperlink ref="G47" r:id="rId338" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J47" r:id="rId339" tooltip="https://www.amazon.it/dp/B0FL7J1HCH?psc=1"/>
+    <hyperlink ref="K47" r:id="rId340" tooltip="https://m.media-amazon.com/images/I/41y3sCvjPcL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId341" tooltip="https://www.amazon.it/dp/B0FL7J1HCH"/>
+    <hyperlink ref="M47" r:id="rId342" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N47" r:id="rId343"/>
+    <hyperlink ref="AW47" r:id="rId344" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9"/>
+    <hyperlink ref="C48" r:id="rId345" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="G48" r:id="rId346" tooltip="https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId347" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L?psc=1"/>
+    <hyperlink ref="K48" r:id="rId348" tooltip="https://images-na.ssl-images-amazon.com/images/I/71VDmFvdOXL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId349" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="M48" r:id="rId350" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N48" r:id="rId351"/>
+    <hyperlink ref="AW48" r:id="rId352" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
+    <hyperlink ref="C49" r:id="rId353" tooltip="https://www.amazon.it/dp/B0H9PTVK8F"/>
+    <hyperlink ref="G49" r:id="rId354" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H9PTVK8F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId355" tooltip="https://www.amazon.it/dp/B0H9PTVK8F?psc=1"/>
+    <hyperlink ref="K49" r:id="rId356" tooltip="https://m.media-amazon.com/images/I/415pkUI3CGL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId357" tooltip="https://www.amazon.it/dp/B0H9PTVK8F"/>
+    <hyperlink ref="M49" r:id="rId358" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="AW49" r:id="rId359" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
   </hyperlinks>
-  <drawing r:id="rId375"/>
+  <drawing r:id="rId360"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19255,18 +18664,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>4814</v>
+        <v>3968</v>
       </c>
       <c r="C2" s="15">
-        <v>575148</v>
+        <v>562466</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>119.47403406730369</v>
+        <v>141.75050403225808</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3561968183499815</v>
+        <v>0.31683168316831684</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19287,7 +18696,7 @@
         <v>100.15894039735099</v>
       </c>
       <c r="G3" s="22">
-        <v>0.12290048094709582</v>
+        <v>0.13262535931012456</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19308,7 +18717,7 @@
         <v>113.66597510373444</v>
       </c>
       <c r="G4" s="22">
-        <v>0.10699223085460599</v>
+        <v>0.11545832002555094</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19329,7 +18738,7 @@
         <v>61.7197549770291</v>
       </c>
       <c r="G5" s="22">
-        <v>0.09663337032926378</v>
+        <v>0.10427978281699138</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19350,7 +18759,7 @@
         <v>212.76785714285714</v>
       </c>
       <c r="G6" s="22">
-        <v>0.02486126526082131</v>
+        <v>0.02682848930054296</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19371,7 +18780,7 @@
         <v>116.79640718562874</v>
       </c>
       <c r="G7" s="22">
-        <v>0.03706992230854606</v>
+        <v>0.04000319386777387</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19392,7 +18801,7 @@
         <v>189.98969072164948</v>
       </c>
       <c r="G8" s="22">
-        <v>0.02153163152053274</v>
+        <v>0.023235388054934525</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19413,7 +18822,7 @@
         <v>96.11482254697286</v>
       </c>
       <c r="G9" s="22">
-        <v>0.03544210136884943</v>
+        <v>0.03824656659214309</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19434,7 +18843,7 @@
         <v>65.98911070780399</v>
       </c>
       <c r="G10" s="22">
-        <v>0.040769515353311137</v>
+        <v>0.04399552858511658</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19455,7 +18864,7 @@
         <v>199.98684210526315</v>
       </c>
       <c r="G11" s="22">
-        <v>0.011246762856085831</v>
+        <v>0.012136697540721815</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19476,7 +18885,7 @@
         <v>85.48870056497175</v>
       </c>
       <c r="G12" s="22">
-        <v>0.026193118756936737</v>
+        <v>0.02826572979878633</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19497,7 +18906,7 @@
         <v>109.9908256880734</v>
       </c>
       <c r="G13" s="22">
-        <v>0.01613022567517573</v>
+        <v>0.01740657936761418</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19518,7 +18927,7 @@
         <v>60.5821325648415</v>
       </c>
       <c r="G14" s="22">
-        <v>0.025675175730669627</v>
+        <v>0.027706802938358352</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19539,7 +18948,7 @@
         <v>137.19333333333333</v>
       </c>
       <c r="G15" s="22">
-        <v>0.011098779134295227</v>
+        <v>0.011977004152028107</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19560,7 +18969,7 @@
         <v>139.3</v>
       </c>
       <c r="G16" s="22">
-        <v>0.010358860525342212</v>
+        <v>0.011178537208559566</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19581,7 +18990,7 @@
         <v>113.66176470588235</v>
       </c>
       <c r="G17" s="22">
-        <v>0.010062893081761006</v>
+        <v>0.01085915043117215</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19602,7 +19011,7 @@
         <v>113.9765625</v>
       </c>
       <c r="G18" s="22">
-        <v>0.009470958194598594</v>
+        <v>0.010220376876397317</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19623,7 +19032,7 @@
         <v>79.9037037037037</v>
       </c>
       <c r="G19" s="22">
-        <v>0.009988901220865706</v>
+        <v>0.010779303736825296</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19644,7 +19053,7 @@
         <v>65.99065420560747</v>
       </c>
       <c r="G20" s="22">
-        <v>0.007917129115797263</v>
+        <v>0.008543596295113382</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19665,7 +19074,7 @@
         <v>140.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0036256011838697744</v>
+        <v>0.003912488022995848</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19686,49 +19095,28 @@
         <v>87.67647058823529</v>
       </c>
       <c r="G22" s="22">
-        <v>0.005031446540880503</v>
+        <v>0.005429575215586075</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>ICARE</t>
         </is>
       </c>
       <c r="B23" s="15">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="C23" s="15">
-        <v>2175</v>
+        <v>80</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="20">
-        <v>15.0</v>
+        <v>80.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.01072881982981872</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>ICARE</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <v>1</v>
-      </c>
-      <c r="C24" s="15">
-        <v>80</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="20">
-        <v>80.0</v>
-      </c>
-      <c r="G24" s="22">
-        <v>7.399186089530152e-05</v>
+        <v>7.984669434685404e-05</v>
       </c>
     </row>
   </sheetData>
@@ -19739,7 +19127,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19792,18 +19180,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>9046</v>
+        <v>8200</v>
       </c>
       <c r="C2" s="15">
-        <v>1068546</v>
+        <v>1055864</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>118.12359053725403</v>
+        <v>128.76390243902438</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6693303736588975</v>
+        <v>0.6547428936442031</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19824,7 +19212,7 @@
         <v>61.7197549770291</v>
       </c>
       <c r="G3" s="22">
-        <v>0.09663337032926378</v>
+        <v>0.10427978281699138</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19845,7 +19233,7 @@
         <v>189.98969072164948</v>
       </c>
       <c r="G4" s="22">
-        <v>0.02153163152053274</v>
+        <v>0.023235388054934525</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19866,7 +19254,7 @@
         <v>65.98911070780399</v>
       </c>
       <c r="G5" s="22">
-        <v>0.040769515353311137</v>
+        <v>0.04399552858511658</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19887,7 +19275,7 @@
         <v>512.695652173913</v>
       </c>
       <c r="G6" s="22">
-        <v>0.005105438401775805</v>
+        <v>0.005509421909932929</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19908,7 +19296,7 @@
         <v>85.48870056497175</v>
       </c>
       <c r="G7" s="22">
-        <v>0.026193118756936737</v>
+        <v>0.02826572979878633</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19929,7 +19317,7 @@
         <v>109.9908256880734</v>
       </c>
       <c r="G8" s="22">
-        <v>0.01613022567517573</v>
+        <v>0.01740657936761418</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19950,7 +19338,7 @@
         <v>60.5821325648415</v>
       </c>
       <c r="G9" s="22">
-        <v>0.025675175730669627</v>
+        <v>0.027706802938358352</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19971,7 +19359,7 @@
         <v>89.9908256880734</v>
       </c>
       <c r="G10" s="22">
-        <v>0.01613022567517573</v>
+        <v>0.01740657936761418</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19992,7 +19380,7 @@
         <v>89.99019607843137</v>
       </c>
       <c r="G11" s="22">
-        <v>0.01509433962264151</v>
+        <v>0.016288725646758224</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20013,7 +19401,7 @@
         <v>113.66176470588235</v>
       </c>
       <c r="G12" s="22">
-        <v>0.010062893081761006</v>
+        <v>0.01085915043117215</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20034,7 +19422,7 @@
         <v>113.9765625</v>
       </c>
       <c r="G13" s="22">
-        <v>0.009470958194598594</v>
+        <v>0.010220376876397317</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20055,7 +19443,7 @@
         <v>99.992</v>
       </c>
       <c r="G14" s="22">
-        <v>0.00924898261191269</v>
+        <v>0.009980836793356755</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20076,7 +19464,7 @@
         <v>79.9037037037037</v>
       </c>
       <c r="G15" s="22">
-        <v>0.009988901220865706</v>
+        <v>0.010779303736825296</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20097,7 +19485,7 @@
         <v>65.99065420560747</v>
       </c>
       <c r="G16" s="22">
-        <v>0.007917129115797263</v>
+        <v>0.008543596295113382</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20118,7 +19506,7 @@
         <v>140.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0036256011838697744</v>
+        <v>0.003912488022995848</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20139,91 +19527,70 @@
         <v>200.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0010358860525342213</v>
+        <v>0.0011178537208559566</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>HOORAY Group</t>
         </is>
       </c>
       <c r="B19" s="15">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="C19" s="15">
-        <v>2175</v>
+        <v>951</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="20">
-        <v>15.0</v>
+        <v>13.985294117647058</v>
       </c>
       <c r="G19" s="22">
-        <v>0.01072881982981872</v>
+        <v>0.005429575215586075</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>HOORAY Group</t>
+          <t>Cecotec Italy</t>
         </is>
       </c>
       <c r="B20" s="15">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C20" s="15">
-        <v>951</v>
+        <v>210</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="20">
-        <v>13.985294117647058</v>
+        <v>70.0</v>
       </c>
       <c r="G20" s="22">
-        <v>0.005031446540880503</v>
+        <v>0.0002395400830405621</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Italy</t>
+          <t>VIVARALimited</t>
         </is>
       </c>
       <c r="B21" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" s="15">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="20">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.00022197558268590456</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>VIVARALimited</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>1</v>
-      </c>
-      <c r="C22" s="15">
-        <v>80</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20">
-        <v>80.0</v>
-      </c>
-      <c r="G22" s="22">
-        <v>7.399186089530152e-05</v>
+        <v>7.984669434685404e-05</v>
       </c>
     </row>
   </sheetData>
